--- a/data/trans_orig/P04C04_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>442828</t>
+          <t>442834</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>470428</t>
+          <t>469590</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>651483</t>
+          <t>650935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>679278</t>
+          <t>679837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1103686</t>
+          <t>1103133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1141855</t>
+          <t>1142571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>34676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>29548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53036</t>
+          <t>52679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64733</t>
+          <t>63834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90209</t>
+          <t>91093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>101141</t>
+          <t>100346</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136281</t>
+          <t>136036</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1148099</t>
+          <t>1185588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1955721</t>
+          <t>1959382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1689602</t>
+          <t>1684478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1970550</t>
+          <t>1968537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2967442</t>
+          <t>2904657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3890424</t>
+          <t>3883194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32212</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59056</t>
+          <t>56550</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>307952</t>
+          <t>307646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1128142</t>
+          <t>1091727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>247025</t>
+          <t>248117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>534175</t>
+          <t>534467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>595598</t>
+          <t>601749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1525466</t>
+          <t>1585585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>487479</t>
+          <t>485667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>537392</t>
+          <t>537427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>516767</t>
+          <t>516858</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>548352</t>
+          <t>549179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1015237</t>
+          <t>1013216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073935</t>
+          <t>1073521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>27741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99930</t>
+          <t>99827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146657</t>
+          <t>151365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100636</t>
+          <t>100042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132328</t>
+          <t>130706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>213387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268150</t>
+          <t>270813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2100786</t>
+          <t>2152281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2936270</t>
+          <t>2935884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2900830</t>
+          <t>2886474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3167868</t>
+          <t>3173154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5110435</t>
+          <t>5043267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6057822</t>
+          <t>6046460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63570</t>
+          <t>64094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52837</t>
+          <t>52093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>61746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99798</t>
+          <t>103778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464833</t>
+          <t>464416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1311306</t>
+          <t>1265591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>441080</t>
+          <t>435896</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>711468</t>
+          <t>731109</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>945743</t>
+          <t>961038</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1908468</t>
+          <t>1967875</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C04_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>457851</t>
+          <t>514097</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>442834</t>
+          <t>498219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>469590</t>
+          <t>527812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>665948</t>
+          <t>723254</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>650935</t>
+          <t>708253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>679837</t>
+          <t>736490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1123798</t>
+          <t>1237351</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1103133</t>
+          <t>1216143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1142571</t>
+          <t>1257188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>19119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>45991</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52679</t>
+          <t>60189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76068</t>
+          <t>83083</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63834</t>
+          <t>71324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91093</t>
+          <t>97811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116015</t>
+          <t>129074</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100346</t>
+          <t>110493</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136036</t>
+          <t>148567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>511450</t>
+          <t>574904</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>511450</t>
+          <t>574904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>511450</t>
+          <t>574904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>752651</t>
+          <t>818837</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>752651</t>
+          <t>818837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>752651</t>
+          <t>818837</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1264101</t>
+          <t>1393741</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1264101</t>
+          <t>1393741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1264101</t>
+          <t>1393741</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1737345</t>
+          <t>1896051</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1185588</t>
+          <t>1853360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1959382</t>
+          <t>1935471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1883459</t>
+          <t>1852102</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1684478</t>
+          <t>1820409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1968537</t>
+          <t>1880233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3620805</t>
+          <t>3748153</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2904657</t>
+          <t>3695187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3883194</t>
+          <t>3798345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37831</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29675</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>38639</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26248</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56550</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>530619</t>
+          <t>306483</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>307646</t>
+          <t>267355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1091727</t>
+          <t>348221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>331871</t>
+          <t>295189</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>248117</t>
+          <t>269906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>534467</t>
+          <t>325476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>862490</t>
+          <t>601672</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>601749</t>
+          <t>551053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1585585</t>
+          <t>650789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2288071</t>
+          <t>2226665</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2288071</t>
+          <t>2226665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2288071</t>
+          <t>2226665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2233862</t>
+          <t>2167264</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2233862</t>
+          <t>2167264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2233862</t>
+          <t>2167264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4521934</t>
+          <t>4393929</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4521934</t>
+          <t>4393929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4521934</t>
+          <t>4393929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>515210</t>
+          <t>572778</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>485667</t>
+          <t>551076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>537427</t>
+          <t>593166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>533454</t>
+          <t>589664</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>516858</t>
+          <t>570429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>549179</t>
+          <t>605592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1048665</t>
+          <t>1162443</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1013216</t>
+          <t>1133161</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073521</t>
+          <t>1190838</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,22 +1785,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>121225</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99827</t>
+          <t>108886</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151365</t>
+          <t>149091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>115416</t>
+          <t>131521</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100042</t>
+          <t>114938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130706</t>
+          <t>151288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>236641</t>
+          <t>259809</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213387</t>
+          <t>231769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270813</t>
+          <t>287252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>644983</t>
+          <t>710052</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>644983</t>
+          <t>710052</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>644983</t>
+          <t>710052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>657299</t>
+          <t>730803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>657299</t>
+          <t>730803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>657299</t>
+          <t>730803</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1302283</t>
+          <t>1440855</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1302283</t>
+          <t>1440855</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1302283</t>
+          <t>1440855</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2710406</t>
+          <t>2982926</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2152281</t>
+          <t>2930883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2935884</t>
+          <t>3034020</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3082862</t>
+          <t>3165021</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2886474</t>
+          <t>3129403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3173154</t>
+          <t>3200288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5793268</t>
+          <t>6147947</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5043267</t>
+          <t>6089430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6046460</t>
+          <t>6208537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42307</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>33930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64094</t>
+          <t>67283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>32138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52093</t>
+          <t>57121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>79903</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61746</t>
+          <t>72306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103778</t>
+          <t>114128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>691791</t>
+          <t>480761</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464416</t>
+          <t>432239</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1265591</t>
+          <t>531353</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>523355</t>
+          <t>509794</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>435896</t>
+          <t>473626</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>731109</t>
+          <t>544668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1215146</t>
+          <t>990555</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>961038</t>
+          <t>930734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1967875</t>
+          <t>1047683</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3444504</t>
+          <t>3511621</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3444504</t>
+          <t>3511621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3444504</t>
+          <t>3511621</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3643813</t>
+          <t>3716905</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3643813</t>
+          <t>3716905</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3643813</t>
+          <t>3716905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7088317</t>
+          <t>7228526</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7088317</t>
+          <t>7228526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7088317</t>
+          <t>7228526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
